--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="OC ago-2026" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -549,7 +549,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -610,7 +610,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -732,7 +732,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1037,7 +1037,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1098,7 +1098,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -1159,7 +1159,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1281,7 +1281,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1342,7 +1342,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1525,7 +1525,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1708,7 +1708,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1769,7 +1769,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1952,7 +1952,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -2135,7 +2135,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -2257,7 +2257,7 @@
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -2318,7 +2318,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -2379,7 +2379,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -2440,7 +2440,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2623,7 +2623,7 @@
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2928,7 +2928,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2989,7 +2989,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -3050,7 +3050,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -3172,7 +3172,7 @@
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -3233,7 +3233,7 @@
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -3294,7 +3294,7 @@
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
@@ -3355,7 +3355,7 @@
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
@@ -3416,7 +3416,7 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -3477,7 +3477,7 @@
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -3660,7 +3660,7 @@
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
@@ -3721,7 +3721,7 @@
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
@@ -3843,7 +3843,7 @@
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
@@ -3904,7 +3904,7 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
@@ -3965,7 +3965,7 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
@@ -4087,7 +4087,7 @@
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
@@ -4209,7 +4209,7 @@
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
@@ -4270,7 +4270,7 @@
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -4331,7 +4331,7 @@
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
@@ -4453,7 +4453,7 @@
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
@@ -4514,7 +4514,7 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
@@ -4575,7 +4575,7 @@
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
@@ -4636,7 +4636,7 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
@@ -4697,7 +4697,7 @@
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
@@ -4758,7 +4758,7 @@
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
@@ -5002,7 +5002,7 @@
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
@@ -5063,7 +5063,7 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -5185,7 +5185,7 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
@@ -5246,7 +5246,7 @@
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
@@ -5490,7 +5490,7 @@
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
@@ -5673,7 +5673,7 @@
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
@@ -5734,7 +5734,7 @@
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
@@ -5795,7 +5795,7 @@
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
@@ -5856,7 +5856,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -5978,7 +5978,7 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
@@ -6039,7 +6039,7 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
@@ -6283,7 +6283,7 @@
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
@@ -6344,7 +6344,7 @@
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
@@ -6405,7 +6405,7 @@
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
@@ -6466,7 +6466,7 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
@@ -6481,7 +6481,7 @@
       </c>
       <c r="K99" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
@@ -6531,7 +6531,7 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
@@ -6592,7 +6592,7 @@
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Región Aysén del General Carlos Ibáñez del Campo</t>
+          <t>Aysén</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
@@ -6653,7 +6653,7 @@
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>Región de Magallanes y de la Antártica</t>
+          <t>Magallanes</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
@@ -6775,7 +6775,7 @@
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
@@ -6958,7 +6958,7 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
@@ -7019,7 +7019,7 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -7141,7 +7141,7 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
@@ -7202,7 +7202,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -7263,7 +7263,7 @@
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
@@ -7324,7 +7324,7 @@
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Tarapacá  </t>
+          <t>Tarapacá</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
@@ -7446,7 +7446,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
@@ -7568,7 +7568,7 @@
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
@@ -7629,7 +7629,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -7690,7 +7690,7 @@
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
@@ -7751,7 +7751,7 @@
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
@@ -7812,7 +7812,7 @@
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -7873,7 +7873,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7934,7 +7934,7 @@
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -8056,7 +8056,7 @@
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -8117,7 +8117,7 @@
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
@@ -8178,7 +8178,7 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
@@ -8239,7 +8239,7 @@
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
@@ -8361,7 +8361,7 @@
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -8422,7 +8422,7 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
@@ -8483,7 +8483,7 @@
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
@@ -8498,7 +8498,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -8548,7 +8548,7 @@
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
@@ -8609,7 +8609,7 @@
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -8670,7 +8670,7 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
@@ -8731,7 +8731,7 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -8792,7 +8792,7 @@
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
@@ -8853,7 +8853,7 @@
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -8914,7 +8914,7 @@
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
@@ -9097,7 +9097,7 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -9158,7 +9158,7 @@
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
@@ -9219,7 +9219,7 @@
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
@@ -9280,7 +9280,7 @@
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I145" t="inlineStr">
@@ -9341,7 +9341,7 @@
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
@@ -9463,7 +9463,7 @@
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
@@ -9524,7 +9524,7 @@
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
@@ -9585,7 +9585,7 @@
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
@@ -9646,7 +9646,7 @@
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
@@ -9768,7 +9768,7 @@
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
@@ -9829,7 +9829,7 @@
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
@@ -9890,7 +9890,7 @@
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I155" t="inlineStr">
@@ -9951,7 +9951,7 @@
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -10012,7 +10012,7 @@
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
@@ -10073,7 +10073,7 @@
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I158" t="inlineStr">
@@ -10134,7 +10134,7 @@
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
@@ -10195,7 +10195,7 @@
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I160" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10317,7 +10317,7 @@
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
@@ -10378,7 +10378,7 @@
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I163" t="inlineStr">
@@ -10439,7 +10439,7 @@
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
@@ -10622,7 +10622,7 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I168" t="inlineStr">
@@ -10744,7 +10744,7 @@
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I169" t="inlineStr">
@@ -10805,7 +10805,7 @@
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
@@ -10866,7 +10866,7 @@
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
@@ -10927,7 +10927,7 @@
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
@@ -10988,7 +10988,7 @@
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
@@ -11003,7 +11003,7 @@
       </c>
       <c r="K173" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L173" t="inlineStr">
@@ -11053,7 +11053,7 @@
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
@@ -11114,7 +11114,7 @@
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
@@ -11175,7 +11175,7 @@
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
@@ -11236,7 +11236,7 @@
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
@@ -11297,7 +11297,7 @@
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
@@ -11358,7 +11358,7 @@
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
@@ -11419,7 +11419,7 @@
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
@@ -11480,7 +11480,7 @@
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
@@ -11541,7 +11541,7 @@
       </c>
       <c r="H182" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I182" t="inlineStr">
@@ -11602,7 +11602,7 @@
       </c>
       <c r="H183" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I183" t="inlineStr">
@@ -11663,7 +11663,7 @@
       </c>
       <c r="H184" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I184" t="inlineStr">
@@ -11724,7 +11724,7 @@
       </c>
       <c r="H185" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I185" t="inlineStr">
@@ -11785,7 +11785,7 @@
       </c>
       <c r="H186" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I186" t="inlineStr">
@@ -11846,7 +11846,7 @@
       </c>
       <c r="H187" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I187" t="inlineStr">
@@ -11907,7 +11907,7 @@
       </c>
       <c r="H188" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I188" t="inlineStr">
@@ -11968,7 +11968,7 @@
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
@@ -12029,7 +12029,7 @@
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
@@ -12090,7 +12090,7 @@
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
@@ -12151,7 +12151,7 @@
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
@@ -12212,7 +12212,7 @@
       </c>
       <c r="H193" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I193" t="inlineStr">
@@ -12273,7 +12273,7 @@
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
@@ -12395,7 +12395,7 @@
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
@@ -12456,7 +12456,7 @@
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
@@ -12517,7 +12517,7 @@
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
@@ -12578,7 +12578,7 @@
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
@@ -12639,7 +12639,7 @@
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -12700,7 +12700,7 @@
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
@@ -12761,7 +12761,7 @@
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -12822,7 +12822,7 @@
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
@@ -12883,7 +12883,7 @@
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
@@ -12944,7 +12944,7 @@
       </c>
       <c r="H205" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I205" t="inlineStr">
@@ -13005,7 +13005,7 @@
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
@@ -13066,7 +13066,7 @@
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
@@ -13127,7 +13127,7 @@
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
@@ -13188,7 +13188,7 @@
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
@@ -13249,7 +13249,7 @@
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
@@ -13493,7 +13493,7 @@
       </c>
       <c r="H214" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I214" t="inlineStr">
@@ -13554,7 +13554,7 @@
       </c>
       <c r="H215" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I215" t="inlineStr">
@@ -13615,7 +13615,7 @@
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
@@ -13676,7 +13676,7 @@
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
@@ -13737,7 +13737,7 @@
       </c>
       <c r="H218" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I218" t="inlineStr">
@@ -13798,7 +13798,7 @@
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
@@ -13859,7 +13859,7 @@
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
@@ -13920,7 +13920,7 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I221" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
@@ -14042,7 +14042,7 @@
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
@@ -14103,7 +14103,7 @@
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="H225" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I225" t="inlineStr">
@@ -14225,7 +14225,7 @@
       </c>
       <c r="H226" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I226" t="inlineStr">
@@ -14286,7 +14286,7 @@
       </c>
       <c r="H227" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I227" t="inlineStr">
@@ -14347,7 +14347,7 @@
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
@@ -14408,7 +14408,7 @@
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
@@ -14469,7 +14469,7 @@
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
@@ -14530,7 +14530,7 @@
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
@@ -14652,7 +14652,7 @@
       </c>
       <c r="H233" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I233" t="inlineStr">
@@ -14713,7 +14713,7 @@
       </c>
       <c r="H234" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I234" t="inlineStr">
@@ -14835,7 +14835,7 @@
       </c>
       <c r="H236" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I236" t="inlineStr">
@@ -14896,7 +14896,7 @@
       </c>
       <c r="H237" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I237" t="inlineStr">
@@ -14957,7 +14957,7 @@
       </c>
       <c r="H238" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I238" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="H239" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I239" t="inlineStr">
@@ -15079,7 +15079,7 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I240" t="inlineStr">
@@ -15140,7 +15140,7 @@
       </c>
       <c r="H241" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I241" t="inlineStr">
@@ -15201,7 +15201,7 @@
       </c>
       <c r="H242" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I242" t="inlineStr">
@@ -15262,7 +15262,7 @@
       </c>
       <c r="H243" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I243" t="inlineStr">
@@ -15323,7 +15323,7 @@
       </c>
       <c r="H244" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I244" t="inlineStr">
@@ -15384,7 +15384,7 @@
       </c>
       <c r="H245" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I245" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="H246" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I246" t="inlineStr">
@@ -15460,7 +15460,7 @@
       </c>
       <c r="K246" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L246" t="inlineStr">
@@ -15510,7 +15510,7 @@
       </c>
       <c r="H247" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I247" t="inlineStr">
@@ -15571,7 +15571,7 @@
       </c>
       <c r="H248" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I248" t="inlineStr">
@@ -15632,7 +15632,7 @@
       </c>
       <c r="H249" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I249" t="inlineStr">
@@ -15693,7 +15693,7 @@
       </c>
       <c r="H250" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I250" t="inlineStr">
@@ -15754,7 +15754,7 @@
       </c>
       <c r="H251" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I251" t="inlineStr">
@@ -15815,7 +15815,7 @@
       </c>
       <c r="H252" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I252" t="inlineStr">
@@ -15876,7 +15876,7 @@
       </c>
       <c r="H253" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I253" t="inlineStr">
@@ -15937,7 +15937,7 @@
       </c>
       <c r="H254" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I254" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="H255" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I255" t="inlineStr">
@@ -16059,7 +16059,7 @@
       </c>
       <c r="H256" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I256" t="inlineStr">
@@ -16120,7 +16120,7 @@
       </c>
       <c r="H257" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I257" t="inlineStr">
@@ -16181,7 +16181,7 @@
       </c>
       <c r="H258" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I258" t="inlineStr">
@@ -16242,7 +16242,7 @@
       </c>
       <c r="H259" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I259" t="inlineStr">
@@ -16303,7 +16303,7 @@
       </c>
       <c r="H260" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I260" t="inlineStr">
@@ -16364,7 +16364,7 @@
       </c>
       <c r="H261" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I261" t="inlineStr">
@@ -16425,7 +16425,7 @@
       </c>
       <c r="H262" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I262" t="inlineStr">
@@ -16486,7 +16486,7 @@
       </c>
       <c r="H263" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I263" t="inlineStr">
@@ -16547,7 +16547,7 @@
       </c>
       <c r="H264" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I264" t="inlineStr">
@@ -16608,7 +16608,7 @@
       </c>
       <c r="H265" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I265" t="inlineStr">
@@ -16730,7 +16730,7 @@
       </c>
       <c r="H267" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I267" t="inlineStr">
@@ -16791,7 +16791,7 @@
       </c>
       <c r="H268" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I268" t="inlineStr">
@@ -16852,7 +16852,7 @@
       </c>
       <c r="H269" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I269" t="inlineStr">
@@ -16913,7 +16913,7 @@
       </c>
       <c r="H270" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I270" t="inlineStr">
@@ -16974,7 +16974,7 @@
       </c>
       <c r="H271" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I271" t="inlineStr">
@@ -17035,7 +17035,7 @@
       </c>
       <c r="H272" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I272" t="inlineStr">
@@ -17096,7 +17096,7 @@
       </c>
       <c r="H273" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I273" t="inlineStr">
@@ -17157,7 +17157,7 @@
       </c>
       <c r="H274" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I274" t="inlineStr">
@@ -17218,7 +17218,7 @@
       </c>
       <c r="H275" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I275" t="inlineStr">
@@ -17279,7 +17279,7 @@
       </c>
       <c r="H276" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I276" t="inlineStr">
@@ -17401,7 +17401,7 @@
       </c>
       <c r="H278" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I278" t="inlineStr">
@@ -17462,7 +17462,7 @@
       </c>
       <c r="H279" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I279" t="inlineStr">
@@ -17523,7 +17523,7 @@
       </c>
       <c r="H280" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Maule </t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I280" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="H281" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I281" t="inlineStr">
@@ -17645,7 +17645,7 @@
       </c>
       <c r="H282" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I282" t="inlineStr">
@@ -17706,7 +17706,7 @@
       </c>
       <c r="H283" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I283" t="inlineStr">
@@ -17767,7 +17767,7 @@
       </c>
       <c r="H284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I284" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="K284" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L284" t="inlineStr">
@@ -17832,7 +17832,7 @@
       </c>
       <c r="H285" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I285" t="inlineStr">
@@ -17893,7 +17893,7 @@
       </c>
       <c r="H286" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I286" t="inlineStr">
@@ -18015,7 +18015,7 @@
       </c>
       <c r="H288" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I288" t="inlineStr">
@@ -18076,7 +18076,7 @@
       </c>
       <c r="H289" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I289" t="inlineStr">
@@ -18137,7 +18137,7 @@
       </c>
       <c r="H290" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I290" t="inlineStr">
@@ -18198,7 +18198,7 @@
       </c>
       <c r="H291" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de la Araucanía </t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I291" t="inlineStr">
@@ -18259,7 +18259,7 @@
       </c>
       <c r="H292" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I292" t="inlineStr">
@@ -18381,7 +18381,7 @@
       </c>
       <c r="H294" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I294" t="inlineStr">
@@ -18442,7 +18442,7 @@
       </c>
       <c r="H295" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I295" t="inlineStr">
@@ -18503,7 +18503,7 @@
       </c>
       <c r="H296" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I296" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I297" t="inlineStr">
@@ -18625,7 +18625,7 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I298" t="inlineStr">
@@ -18686,7 +18686,7 @@
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I299" t="inlineStr">
@@ -18747,7 +18747,7 @@
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Antofagasta </t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I300" t="inlineStr">
@@ -18808,7 +18808,7 @@
       </c>
       <c r="H301" t="inlineStr">
         <is>
-          <t>Región de Los Ríos</t>
+          <t>Los Ríos</t>
         </is>
       </c>
       <c r="I301" t="inlineStr">
@@ -18869,7 +18869,7 @@
       </c>
       <c r="H302" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I302" t="inlineStr">
@@ -18930,7 +18930,7 @@
       </c>
       <c r="H303" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I303" t="inlineStr">
@@ -18991,7 +18991,7 @@
       </c>
       <c r="H304" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I304" t="inlineStr">
@@ -19052,7 +19052,7 @@
       </c>
       <c r="H305" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I305" t="inlineStr">
@@ -19113,7 +19113,7 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I306" t="inlineStr">
@@ -19174,7 +19174,7 @@
       </c>
       <c r="H307" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I307" t="inlineStr">
@@ -19235,7 +19235,7 @@
       </c>
       <c r="H308" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I308" t="inlineStr">
@@ -19296,7 +19296,7 @@
       </c>
       <c r="H309" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Atacama </t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I309" t="inlineStr">
@@ -19357,7 +19357,7 @@
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I310" t="inlineStr">
@@ -19418,7 +19418,7 @@
       </c>
       <c r="H311" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I311" t="inlineStr">
@@ -19479,7 +19479,7 @@
       </c>
       <c r="H312" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I312" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="H313" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I313" t="inlineStr">
@@ -19601,7 +19601,7 @@
       </c>
       <c r="H314" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I314" t="inlineStr">
@@ -19662,7 +19662,7 @@
       </c>
       <c r="H315" t="inlineStr">
         <is>
-          <t>Región del Ñuble</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I315" t="inlineStr">
@@ -19723,7 +19723,7 @@
       </c>
       <c r="H316" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I316" t="inlineStr">
@@ -19784,7 +19784,7 @@
       </c>
       <c r="H317" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Coquimbo </t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I317" t="inlineStr">
@@ -19845,7 +19845,7 @@
       </c>
       <c r="H318" t="inlineStr">
         <is>
-          <t>Región de Arica y Parinacota</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I318" t="inlineStr">
@@ -19967,7 +19967,7 @@
       </c>
       <c r="H320" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I320" t="inlineStr">
@@ -20028,7 +20028,7 @@
       </c>
       <c r="H321" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de Valparaíso </t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I321" t="inlineStr">
@@ -20089,7 +20089,7 @@
       </c>
       <c r="H322" t="inlineStr">
         <is>
-          <t>Región del Libertador General Bernardo O´Higgins</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I322" t="inlineStr">
@@ -20211,7 +20211,7 @@
       </c>
       <c r="H324" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región del Biobío </t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I324" t="inlineStr">
@@ -20272,7 +20272,7 @@
       </c>
       <c r="H325" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I325" t="inlineStr">
@@ -20333,7 +20333,7 @@
       </c>
       <c r="H326" t="inlineStr">
         <is>
-          <t>Región Metropolitana de Santiago</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I326" t="inlineStr">
@@ -20394,7 +20394,7 @@
       </c>
       <c r="H327" t="inlineStr">
         <is>
-          <t xml:space="preserve">Región de los Lagos </t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I327" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -2547,7 +2547,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -4743,7 +4743,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -6577,7 +6577,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -9875,7 +9875,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -10973,7 +10973,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -11587,7 +11587,7 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -11709,7 +11709,7 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -12502,7 +12502,7 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -13417,7 +13417,7 @@
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -15556,7 +15556,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -15922,7 +15922,7 @@
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -16166,7 +16166,7 @@
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
@@ -16227,7 +16227,7 @@
       </c>
       <c r="E259" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F259" t="inlineStr">
@@ -16532,7 +16532,7 @@
       </c>
       <c r="E264" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F264" t="inlineStr">
@@ -17142,7 +17142,7 @@
       </c>
       <c r="E274" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F274" t="inlineStr">
@@ -17752,7 +17752,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -19464,7 +19464,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">

--- a/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
+++ b/docs/oc-mensuales/venta-y-arriendo-de-computadores-y-accesorios/ago-2026.xlsx
@@ -1245,7 +1245,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -2647,7 +2647,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2708,7 +2708,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -7157,7 +7157,7 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -9156,7 +9156,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -9266,7 +9266,7 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>4491-410-CM26</t>
+          <t>1053139-129-CM26</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -9291,32 +9291,32 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>69.150.501-4</t>
+          <t>70.770.800-k</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PENCO</t>
+          <t>UNIVERSIDAD DE TARAPACA</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J138" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -9325,7 +9325,7 @@
         </is>
       </c>
       <c r="M138" s="2" t="n">
-        <v>22322.02</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="139">
@@ -9546,7 +9546,7 @@
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
@@ -9591,7 +9591,7 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>1053139-129-CM26</t>
+          <t>4491-410-CM26</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -9616,32 +9616,32 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>70.770.800-k</t>
+          <t>69.150.501-4</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TARAPACA</t>
+          <t>I MUNICIPALIDAD DE PENCO</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J143" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K143" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L143" t="inlineStr">
@@ -9650,7 +9650,7 @@
         </is>
       </c>
       <c r="M143" s="2" t="n">
-        <v>995.64</v>
+        <v>22322.02</v>
       </c>
     </row>
     <row r="144">
@@ -9997,7 +9997,7 @@
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
@@ -10107,7 +10107,7 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>2216-427-CM26</t>
+          <t>2665-400-CM26</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -10127,22 +10127,22 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>MOP Dirección General de Concesiones</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -10166,13 +10166,13 @@
         </is>
       </c>
       <c r="M151" s="2" t="n">
-        <v>54537.13</v>
+        <v>8290.969999999999</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>564162-759-CM26</t>
+          <t>2216-427-CM26</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
@@ -10197,12 +10197,12 @@
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>60.911.000-7</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
+          <t>MOP Dirección General de Concesiones</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
@@ -10212,28 +10212,32 @@
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K152" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L152" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M152" s="2" t="n">
-        <v>1487.49</v>
+        <v>54537.13</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>1426037-145-CM26</t>
+          <t>564162-759-CM26</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -10253,17 +10257,17 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>70.941.900-5</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Desarrollo Social de Colina</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
@@ -10273,32 +10277,28 @@
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL DLM SPA</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
         <is>
-          <t>77.346.435-9</t>
-        </is>
-      </c>
-      <c r="K153" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M153" s="2" t="n">
-        <v>6153.59</v>
+        <v>1487.49</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>1456835-15-CM26</t>
+          <t>1426037-145-CM26</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -10323,27 +10323,27 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>61.981.430-4</t>
+          <t>70.941.900-5</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
+          <t>Corporación Municipal de Desarrollo Social de Colina</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>SOCIEDAD COMERCIAL DLM SPA</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.346.435-9</t>
         </is>
       </c>
       <c r="K154" t="inlineStr">
@@ -10357,13 +10357,13 @@
         </is>
       </c>
       <c r="M154" s="2" t="n">
-        <v>23205</v>
+        <v>6153.59</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>3134-174-CM26</t>
+          <t>1456835-15-CM26</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
@@ -10388,12 +10388,12 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>61.102.014-7</t>
+          <t>61.981.430-4</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL LITORAL</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="I155" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J155" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K155" t="inlineStr">
@@ -10422,13 +10422,13 @@
         </is>
       </c>
       <c r="M155" s="2" t="n">
-        <v>5706.65</v>
+        <v>23205</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>1233623-521-CM26</t>
+          <t>3134-174-CM26</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -10448,32 +10448,32 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>61.102.014-7</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J156" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K156" t="inlineStr">
@@ -10487,13 +10487,13 @@
         </is>
       </c>
       <c r="M156" s="2" t="n">
-        <v>6218.23</v>
+        <v>5706.65</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>1500443-20-CM26</t>
+          <t>1233623-521-CM26</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -10518,27 +10518,27 @@
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>60.501.000-8</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DEL INTERIOR</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I157" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J157" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K157" t="inlineStr">
@@ -10552,7 +10552,7 @@
         </is>
       </c>
       <c r="M157" s="2" t="n">
-        <v>289.06</v>
+        <v>6218.23</v>
       </c>
     </row>
     <row r="158">
@@ -10619,7 +10619,7 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>1274189-384-CM26</t>
+          <t>3299-300-CM26</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
@@ -10644,32 +10644,32 @@
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>70.934.900-7</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I159" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J159" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K159" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L159" t="inlineStr">
@@ -10678,13 +10678,13 @@
         </is>
       </c>
       <c r="M159" s="2" t="n">
-        <v>8485.889999999999</v>
+        <v>4022.15</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>2483-508-CM26</t>
+          <t>1274189-384-CM26</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
@@ -10704,17 +10704,17 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>69.071.300-4</t>
+          <t>70.934.900-7</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE QUILICURA</t>
+          <t>CORPORACION DE DESARROLLO SOCIAL DE BUIN</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
@@ -10724,12 +10724,12 @@
       </c>
       <c r="I160" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J160" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K160" t="inlineStr">
@@ -10743,13 +10743,13 @@
         </is>
       </c>
       <c r="M160" s="2" t="n">
-        <v>30553.49</v>
+        <v>8485.889999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>1057918-5-CM26</t>
+          <t>2483-508-CM26</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
@@ -10769,22 +10769,22 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>61.606.800-8</t>
+          <t>69.071.300-4</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
+          <t>I MUNICIPALIDAD DE QUILICURA</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I161" t="inlineStr">
@@ -10808,13 +10808,13 @@
         </is>
       </c>
       <c r="M161" s="2" t="n">
-        <v>72140.17999999999</v>
+        <v>30553.49</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>5251-632-CM26</t>
+          <t>1057918-5-CM26</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
@@ -10834,48 +10834,52 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>70.729.100-1</t>
+          <t>61.606.800-8</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
+          <t>SERVICIO DE SALUD LIBERTADOR BDO OHIGGINS</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I162" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J162" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K162" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L162" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M162" s="2" t="n">
-        <v>9086.84</v>
+        <v>72140.17999999999</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>2682-249-CM26</t>
+          <t>5251-632-CM26</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
@@ -10895,17 +10899,17 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>69.255.500-7</t>
+          <t>70.729.100-1</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
+          <t>UNIVERSIDAD TECNOLOGICA METROPOLITANA</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
@@ -10915,32 +10919,28 @@
       </c>
       <c r="I163" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J163" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
-        </is>
-      </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>Ñuble</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M163" s="2" t="n">
-        <v>29799.74</v>
+        <v>9086.84</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>2665-400-CM26</t>
+          <t>2682-249-CM26</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
@@ -10960,37 +10960,37 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>69.255.500-7</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>I MUNICIPALIDAD DE INDEPENDENCIA</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I164" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J164" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K164" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
@@ -10999,13 +10999,13 @@
         </is>
       </c>
       <c r="M164" s="2" t="n">
-        <v>8290.969999999999</v>
+        <v>29799.74</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>3299-300-CM26</t>
+          <t>1500443-20-CM26</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
@@ -11030,32 +11030,32 @@
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>60.501.000-8</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>SUBSECRETARIA DEL INTERIOR</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I165" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J165" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K165" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
@@ -11064,13 +11064,13 @@
         </is>
       </c>
       <c r="M165" s="2" t="n">
-        <v>4022.15</v>
+        <v>289.06</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>1126922-1184-CM26</t>
+          <t>564162-770-CM26</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -11090,32 +11090,32 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>60.911.000-7</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>UNIVERSIDAD DE SANTIAGO DE CHILE</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I166" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>SYSCAM TECHNOLOGIES SPA</t>
         </is>
       </c>
       <c r="J166" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>77.137.827-7</t>
         </is>
       </c>
       <c r="K166" t="inlineStr">
@@ -11129,13 +11129,13 @@
         </is>
       </c>
       <c r="M166" s="2" t="n">
-        <v>6378.4</v>
+        <v>2594.82</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>4928-82-CM26</t>
+          <t>1126922-1184-CM26</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -11160,27 +11160,27 @@
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>61.938.500-4</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I167" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
@@ -11194,13 +11194,13 @@
         </is>
       </c>
       <c r="M167" s="2" t="n">
-        <v>4641</v>
+        <v>6378.4</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>5613-301-CM26</t>
+          <t>4928-82-CM26</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.938.500-4</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
@@ -11240,28 +11240,32 @@
       </c>
       <c r="I168" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J168" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K168" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K168" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L168" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M168" s="2" t="n">
-        <v>306.98</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>515184-4-CM26</t>
+          <t>5613-301-CM26</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -11281,17 +11285,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>61.933.400-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>CENTRO REFERENCIAL DE SALUD DR SALVADOR ALLENDE GOSSENS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
@@ -11301,32 +11305,28 @@
       </c>
       <c r="I169" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J169" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
-        </is>
-      </c>
-      <c r="K169" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K169" t="inlineStr"/>
       <c r="L169" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M169" s="2" t="n">
-        <v>14423.99</v>
+        <v>306.98</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>5839-37-CM26</t>
+          <t>515184-4-CM26</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -11351,43 +11351,47 @@
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>61.933.400-0</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>CENTRO REFERENCIAL DE SALUD DR SALVADOR ALLENDE GOSSENS</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I170" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K170" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K170" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L170" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M170" s="2" t="n">
-        <v>11239.07</v>
+        <v>14423.99</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>2369-75-CM26</t>
+          <t>5839-37-CM26</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -11407,52 +11411,48 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>69.010.100-9</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE ARICA</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I171" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J171" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K171" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K171" t="inlineStr"/>
       <c r="L171" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M171" s="2" t="n">
-        <v>289777.42</v>
+        <v>11239.07</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>1002592-36-CM26</t>
+          <t>2369-75-CM26</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -11477,27 +11477,27 @@
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>65.154.021-6</t>
+          <t>69.010.100-9</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
+          <t>I MUNICIPALIDAD DE ARICA</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I172" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J172" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K172" t="inlineStr">
@@ -11511,13 +11511,13 @@
         </is>
       </c>
       <c r="M172" s="2" t="n">
-        <v>5528.93</v>
+        <v>289777.42</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>1110404-806-CM26</t>
+          <t>1002592-36-CM26</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -11542,27 +11542,27 @@
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>65.154.021-6</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>SERVICIO LOCAL DE EDUCACION LAS BARRANCAS</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I173" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J173" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K173" t="inlineStr">
@@ -11576,13 +11576,13 @@
         </is>
       </c>
       <c r="M173" s="2" t="n">
-        <v>15721.74</v>
+        <v>5528.93</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>654478-196-CM26</t>
+          <t>1110404-806-CM26</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -11607,27 +11607,27 @@
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>61.980.140-7</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I174" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J174" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K174" t="inlineStr">
@@ -11641,13 +11641,13 @@
         </is>
       </c>
       <c r="M174" s="2" t="n">
-        <v>8676.360000000001</v>
+        <v>15721.74</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>4371-329-CM26</t>
+          <t>654478-196-CM26</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -11672,27 +11672,27 @@
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>69.081.000-k</t>
+          <t>61.980.140-7</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
+          <t>SUBSECRETARIA DE PREVENCION DEL DELITO</t>
         </is>
       </c>
       <c r="H175" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I175" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J175" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K175" t="inlineStr">
@@ -11706,13 +11706,13 @@
         </is>
       </c>
       <c r="M175" s="2" t="n">
-        <v>272.32</v>
+        <v>8676.360000000001</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>3474-461-CM26</t>
+          <t>4371-329-CM26</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -11737,27 +11737,27 @@
       </c>
       <c r="F176" t="inlineStr">
         <is>
-          <t>61.979.960-7</t>
+          <t>69.081.000-k</t>
         </is>
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
+          <t>I MUNICIPALIDAD DE SAN VICENTE</t>
         </is>
       </c>
       <c r="H176" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I176" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J176" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K176" t="inlineStr">
@@ -11771,13 +11771,13 @@
         </is>
       </c>
       <c r="M176" s="2" t="n">
-        <v>2110.32</v>
+        <v>272.32</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>3659-720-CM26</t>
+          <t>3474-461-CM26</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -11792,53 +11792,57 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>2026-08-19</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
         <is>
-          <t>69.266.500-7</t>
+          <t>61.979.960-7</t>
         </is>
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
+          <t>DIRECCION DE LOGISTICA DE CARABINEROS</t>
         </is>
       </c>
       <c r="H177" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I177" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J177" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
-        </is>
-      </c>
-      <c r="K177" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K177" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L177" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M177" s="2" t="n">
-        <v>6832.59</v>
+        <v>2110.32</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>1126922-1203-CM26</t>
+          <t>3659-720-CM26</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -11858,52 +11862,48 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
         <is>
-          <t>62.000.800-1</t>
+          <t>69.266.500-7</t>
         </is>
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE CHILLAN VIEJO</t>
         </is>
       </c>
       <c r="H178" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I178" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J178" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K178" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.131.929-9</t>
+        </is>
+      </c>
+      <c r="K178" t="inlineStr"/>
       <c r="L178" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M178" s="2" t="n">
-        <v>6377.38</v>
+        <v>6832.59</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>2594-736-CM26</t>
+          <t>1126922-1203-CM26</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -11923,37 +11923,37 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
         <is>
-          <t>73.568.600-3</t>
+          <t>62.000.800-1</t>
         </is>
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CONCON</t>
+          <t>SERVICIO LOCAL DE EDUCACION PUBLICA DE LLANQUIHUE</t>
         </is>
       </c>
       <c r="H179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I179" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J179" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K179" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
@@ -11962,13 +11962,13 @@
         </is>
       </c>
       <c r="M179" s="2" t="n">
-        <v>4884.47</v>
+        <v>6377.38</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>4239-426-CM26</t>
+          <t>2594-736-CM26</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -11993,32 +11993,32 @@
       </c>
       <c r="F180" t="inlineStr">
         <is>
-          <t>69.160.201-K</t>
+          <t>73.568.600-3</t>
         </is>
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
+          <t>I MUNICIPALIDAD DE CONCON</t>
         </is>
       </c>
       <c r="H180" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I180" t="inlineStr">
         <is>
-          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J180" t="inlineStr">
         <is>
-          <t>96.523.180-3</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K180" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L180" t="inlineStr">
@@ -12027,13 +12027,13 @@
         </is>
       </c>
       <c r="M180" s="2" t="n">
-        <v>31851.65</v>
+        <v>4884.47</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>633-477-CM26</t>
+          <t>4239-426-CM26</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -12053,37 +12053,37 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>69.160.201-K</t>
         </is>
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>I MUNICIPALIDAD DE CURANILAHUE</t>
         </is>
       </c>
       <c r="H181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I181" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>OPCIONES SA SISTEMAS DE INFORMACION</t>
         </is>
       </c>
       <c r="J181" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
+          <t>96.523.180-3</t>
         </is>
       </c>
       <c r="K181" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
@@ -12092,13 +12092,13 @@
         </is>
       </c>
       <c r="M181" s="2" t="n">
-        <v>1345.89</v>
+        <v>31851.65</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>770-112-CM26</t>
+          <t>633-477-CM26</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>60.604.000-8</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H182" t="inlineStr">
@@ -12138,12 +12138,12 @@
       </c>
       <c r="I182" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J182" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K182" t="inlineStr">
@@ -12157,13 +12157,13 @@
         </is>
       </c>
       <c r="M182" s="2" t="n">
-        <v>3691.57</v>
+        <v>1345.89</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>5544-8-CM26</t>
+          <t>770-112-CM26</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -12188,12 +12188,12 @@
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>60.604.000-8</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>Dirección Nacional de Fronteras y Límites del Estado</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -12203,12 +12203,12 @@
       </c>
       <c r="I183" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J183" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K183" t="inlineStr">
@@ -12222,13 +12222,13 @@
         </is>
       </c>
       <c r="M183" s="2" t="n">
-        <v>3718.44</v>
+        <v>3691.57</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>633-476-CM26</t>
+          <t>5544-8-CM26</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
@@ -12253,12 +12253,12 @@
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H184" t="inlineStr">
@@ -12268,12 +12268,12 @@
       </c>
       <c r="I184" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TELENET LTDA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J184" t="inlineStr">
         <is>
-          <t>77.700.780-7</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K184" t="inlineStr">
@@ -12287,13 +12287,13 @@
         </is>
       </c>
       <c r="M184" s="2" t="n">
-        <v>19514.81</v>
+        <v>3718.44</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>5153-1508-CM26</t>
+          <t>633-476-CM26</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -12313,17 +12313,17 @@
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H185" t="inlineStr">
@@ -12333,28 +12333,32 @@
       </c>
       <c r="I185" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>COMERCIALIZADORA TELENET LTDA</t>
         </is>
       </c>
       <c r="J185" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K185" t="inlineStr"/>
+          <t>77.700.780-7</t>
+        </is>
+      </c>
+      <c r="K185" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L185" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M185" s="2" t="n">
-        <v>4604.76</v>
+        <v>19514.81</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>5684-478-CM26</t>
+          <t>5153-1508-CM26</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
@@ -12374,7 +12378,7 @@
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
@@ -12394,12 +12398,12 @@
       </c>
       <c r="I186" t="inlineStr">
         <is>
-          <t>Clevertec</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J186" t="inlineStr">
         <is>
-          <t>76.330.984-3</t>
+          <t>78.885.550-8</t>
         </is>
       </c>
       <c r="K186" t="inlineStr"/>
@@ -12409,13 +12413,13 @@
         </is>
       </c>
       <c r="M186" s="2" t="n">
-        <v>1135.74</v>
+        <v>4604.76</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>5684-477-CM26</t>
+          <t>5684-478-CM26</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -12455,32 +12459,28 @@
       </c>
       <c r="I187" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
+          <t>Clevertec</t>
         </is>
       </c>
       <c r="J187" t="inlineStr">
         <is>
-          <t>76.799.430-3</t>
-        </is>
-      </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.330.984-3</t>
+        </is>
+      </c>
+      <c r="K187" t="inlineStr"/>
       <c r="L187" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M187" s="2" t="n">
-        <v>828.24</v>
+        <v>1135.74</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>5684-476-CM26</t>
+          <t>5684-477-CM26</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -12520,12 +12520,12 @@
       </c>
       <c r="I188" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>COMERCIALIZADORA SP DIGITAL SPA</t>
         </is>
       </c>
       <c r="J188" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>76.799.430-3</t>
         </is>
       </c>
       <c r="K188" t="inlineStr">
@@ -12539,13 +12539,13 @@
         </is>
       </c>
       <c r="M188" s="2" t="n">
-        <v>30617.38</v>
+        <v>828.24</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>557639-1865-CM26</t>
+          <t>5684-476-CM26</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -12565,32 +12565,32 @@
       </c>
       <c r="E189" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F189" t="inlineStr">
         <is>
-          <t>71.014.200-9</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H189" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I189" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J189" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K189" t="inlineStr">
@@ -12604,13 +12604,13 @@
         </is>
       </c>
       <c r="M189" s="2" t="n">
-        <v>15216.23</v>
+        <v>30617.38</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>1480067-83-CM26</t>
+          <t>557639-1865-CM26</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -12635,27 +12635,27 @@
       </c>
       <c r="F190" t="inlineStr">
         <is>
-          <t>69.255.600-3</t>
+          <t>71.014.200-9</t>
         </is>
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VITACURA</t>
+          <t>CORP MUNICIPAL DE SERVICIOS PUBLICOS TRASPASADOS DE RANCAGUA</t>
         </is>
       </c>
       <c r="H190" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I190" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J190" t="inlineStr">
         <is>
-          <t>77.108.316-1</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K190" t="inlineStr">
@@ -12669,13 +12669,13 @@
         </is>
       </c>
       <c r="M190" s="2" t="n">
-        <v>4057.9</v>
+        <v>15216.23</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>3428-230-CM26</t>
+          <t>1480067-83-CM26</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -12695,32 +12695,32 @@
       </c>
       <c r="E191" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F191" t="inlineStr">
         <is>
-          <t>61.948.900-4</t>
+          <t>69.255.600-3</t>
         </is>
       </c>
       <c r="G191" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>I MUNICIPALIDAD DE VITACURA</t>
         </is>
       </c>
       <c r="H191" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I191" t="inlineStr">
         <is>
-          <t>PRODATA S.A</t>
+          <t>BOOKCOMPUTER COMERCIALIZADORA SPA</t>
         </is>
       </c>
       <c r="J191" t="inlineStr">
         <is>
-          <t>79.808.810-6</t>
+          <t>77.108.316-1</t>
         </is>
       </c>
       <c r="K191" t="inlineStr">
@@ -12734,13 +12734,13 @@
         </is>
       </c>
       <c r="M191" s="2" t="n">
-        <v>7011.48</v>
+        <v>4057.9</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>1393495-694-CM26</t>
+          <t>3428-230-CM26</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -12760,32 +12760,32 @@
       </c>
       <c r="E192" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F192" t="inlineStr">
         <is>
-          <t>61.981.080-5</t>
+          <t>61.948.900-4</t>
         </is>
       </c>
       <c r="G192" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H192" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I192" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>PRODATA S.A</t>
         </is>
       </c>
       <c r="J192" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
+          <t>79.808.810-6</t>
         </is>
       </c>
       <c r="K192" t="inlineStr">
@@ -12799,13 +12799,13 @@
         </is>
       </c>
       <c r="M192" s="2" t="n">
-        <v>66973.2</v>
+        <v>7011.48</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>3337-199-CM26</t>
+          <t>1393495-694-CM26</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -12820,22 +12820,22 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>2026-08-20</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F193" t="inlineStr">
         <is>
-          <t>61.101.032-K</t>
+          <t>61.981.080-5</t>
         </is>
       </c>
       <c r="G193" t="inlineStr">
         <is>
-          <t>DIVISION LOGISTICA DEL EJERCITO</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA SANTA CORINA</t>
         </is>
       </c>
       <c r="H193" t="inlineStr">
@@ -12845,28 +12845,32 @@
       </c>
       <c r="I193" t="inlineStr">
         <is>
-          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J193" t="inlineStr">
         <is>
-          <t>76.075.901-5</t>
-        </is>
-      </c>
-      <c r="K193" t="inlineStr"/>
+          <t>96.678.350-8</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L193" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M193" s="2" t="n">
-        <v>91.70999999999999</v>
+        <v>66973.2</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>1110404-822-CM26</t>
+          <t>3337-199-CM26</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -12891,47 +12895,43 @@
       </c>
       <c r="F194" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>61.101.032-K</t>
         </is>
       </c>
       <c r="G194" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>DIVISION LOGISTICA DEL EJERCITO</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I194" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>SOCIEDAD COMERCIAL ISPLUS LIMITADA</t>
         </is>
       </c>
       <c r="J194" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
-        </is>
-      </c>
-      <c r="K194" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.075.901-5</t>
+        </is>
+      </c>
+      <c r="K194" t="inlineStr"/>
       <c r="L194" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M194" s="2" t="n">
-        <v>4287.75</v>
+        <v>91.70999999999999</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>2665-409-CM26</t>
+          <t>1110404-822-CM26</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -12951,37 +12951,37 @@
       </c>
       <c r="E195" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F195" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G195" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H195" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I195" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J195" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K195" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
@@ -12990,13 +12990,13 @@
         </is>
       </c>
       <c r="M195" s="2" t="n">
-        <v>12160.73</v>
+        <v>4287.75</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>1110404-824-CM26</t>
+          <t>2665-409-CM26</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -13016,37 +13016,37 @@
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
         <is>
-          <t>62.000.660-2</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G196" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H196" t="inlineStr">
         <is>
-          <t>Arica y Parinacota</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I196" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J196" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.474.803-2</t>
         </is>
       </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
@@ -13055,13 +13055,13 @@
         </is>
       </c>
       <c r="M196" s="2" t="n">
-        <v>5555.61</v>
+        <v>12160.73</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>3486-425-CM26</t>
+          <t>1110404-824-CM26</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -13081,48 +13081,52 @@
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
         <is>
-          <t>69.190.400-8</t>
+          <t>62.000.660-2</t>
         </is>
       </c>
       <c r="G197" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
+          <t>SERVICIO LOCAL DE EDUCACION DE CHINCHORRO</t>
         </is>
       </c>
       <c r="H197" t="inlineStr">
         <is>
-          <t>Araucanía</t>
+          <t>Arica y Parinacota</t>
         </is>
       </c>
       <c r="I197" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J197" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K197" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K197" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L197" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M197" s="2" t="n">
-        <v>10142.25</v>
+        <v>5555.61</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>5416-846-CM26</t>
+          <t>3486-425-CM26</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -13142,52 +13146,48 @@
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
         <is>
-          <t>70.783.100-6</t>
+          <t>69.190.400-8</t>
         </is>
       </c>
       <c r="G198" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE LA SERENA</t>
+          <t>I MUNICIPALIDAD DE NUEVA IMPERIAL</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>Araucanía</t>
         </is>
       </c>
       <c r="I198" t="inlineStr">
         <is>
-          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J198" t="inlineStr">
         <is>
-          <t>76.128.275-1</t>
-        </is>
-      </c>
-      <c r="K198" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K198" t="inlineStr"/>
       <c r="L198" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M198" s="2" t="n">
-        <v>3415.31</v>
+        <v>10142.25</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>1233623-579-CM26</t>
+          <t>5416-846-CM26</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -13207,37 +13207,37 @@
       </c>
       <c r="E199" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
         <is>
-          <t>61.980.920-3</t>
+          <t>70.783.100-6</t>
         </is>
       </c>
       <c r="G199" t="inlineStr">
         <is>
-          <t>Servicio Local de Educación Pública Licancabur</t>
+          <t>UNIVERSIDAD DE LA SERENA</t>
         </is>
       </c>
       <c r="H199" t="inlineStr">
         <is>
-          <t>Antofagasta</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I199" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>INTEGRACION DE SOLUCIONES LIMITADA</t>
         </is>
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>76.128.275-1</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
@@ -13246,13 +13246,13 @@
         </is>
       </c>
       <c r="M199" s="2" t="n">
-        <v>70768.14999999999</v>
+        <v>3415.31</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>4469-773-CM26</t>
+          <t>1233623-579-CM26</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -13277,17 +13277,17 @@
       </c>
       <c r="F200" t="inlineStr">
         <is>
-          <t>70.754.700-6</t>
+          <t>61.980.920-3</t>
         </is>
       </c>
       <c r="G200" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
+          <t>Servicio Local de Educación Pública Licancabur</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Antofagasta</t>
         </is>
       </c>
       <c r="I200" t="inlineStr">
@@ -13311,13 +13311,13 @@
         </is>
       </c>
       <c r="M200" s="2" t="n">
-        <v>484.93</v>
+        <v>70768.14999999999</v>
       </c>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>2292-6953-CM26</t>
+          <t>4469-773-CM26</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -13337,48 +13337,52 @@
       </c>
       <c r="E201" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F201" t="inlineStr">
         <is>
-          <t>69.110.400-1</t>
+          <t>70.754.700-6</t>
         </is>
       </c>
       <c r="G201" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TALCA</t>
+          <t>UNIVERSIDAD DE PLAYA ANCHA DE CIENCIAS DE LA EDUCACION</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I201" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J201" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K201" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L201" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M201" s="2" t="n">
-        <v>2719.03</v>
+        <v>484.93</v>
       </c>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>2665-408-CM26</t>
+          <t>2292-6953-CM26</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -13398,22 +13402,22 @@
       </c>
       <c r="E202" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F202" t="inlineStr">
         <is>
-          <t>69.150.101-9</t>
+          <t>69.110.400-1</t>
         </is>
       </c>
       <c r="G202" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE TOME</t>
+          <t>I MUNICIPALIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I202" t="inlineStr">
@@ -13433,13 +13437,13 @@
         </is>
       </c>
       <c r="M202" s="2" t="n">
-        <v>8478.51</v>
+        <v>2719.03</v>
       </c>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>5574-72-CM26</t>
+          <t>2665-408-CM26</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -13459,52 +13463,48 @@
       </c>
       <c r="E203" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F203" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.150.101-9</t>
         </is>
       </c>
       <c r="G203" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE TOME</t>
         </is>
       </c>
       <c r="H203" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="I203" t="inlineStr">
         <is>
-          <t>TECHNOSYSTEMS CHILE SPA</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J203" t="inlineStr">
         <is>
-          <t>96.678.350-8</t>
-        </is>
-      </c>
-      <c r="K203" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K203" t="inlineStr"/>
       <c r="L203" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M203" s="2" t="n">
-        <v>49385</v>
+        <v>8478.51</v>
       </c>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>3287-426-CM26</t>
+          <t>5574-72-CM26</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -13524,37 +13524,37 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
         <is>
-          <t>69.100.500-3</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G204" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LICANTEN</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I204" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>TECHNOSYSTEMS CHILE SPA</t>
         </is>
       </c>
       <c r="J204" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>96.678.350-8</t>
         </is>
       </c>
       <c r="K204" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
@@ -13563,13 +13563,13 @@
         </is>
       </c>
       <c r="M204" s="2" t="n">
-        <v>3016.61</v>
+        <v>49385</v>
       </c>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>1469-2347-CM26</t>
+          <t>3287-426-CM26</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="F205" t="inlineStr">
         <is>
-          <t>70.885.500-6</t>
+          <t>69.100.500-3</t>
         </is>
       </c>
       <c r="G205" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE TALCA</t>
+          <t>I MUNICIPALIDAD DE LICANTEN</t>
         </is>
       </c>
       <c r="H205" t="inlineStr">
@@ -13609,28 +13609,32 @@
       </c>
       <c r="I205" t="inlineStr">
         <is>
-          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>76.179.170-2</t>
-        </is>
-      </c>
-      <c r="K205" t="inlineStr"/>
+          <t>96.689.970-0</t>
+        </is>
+      </c>
+      <c r="K205" t="inlineStr">
+        <is>
+          <t>Valparaíso</t>
+        </is>
+      </c>
       <c r="L205" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M205" s="2" t="n">
-        <v>15261.75</v>
+        <v>3016.61</v>
       </c>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>5543-47-CM26</t>
+          <t>1469-2347-CM26</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -13650,52 +13654,48 @@
       </c>
       <c r="E206" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F206" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>70.885.500-6</t>
         </is>
       </c>
       <c r="G206" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>UNIVERSIDAD DE TALCA</t>
         </is>
       </c>
       <c r="H206" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I206" t="inlineStr">
         <is>
-          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
+          <t>SOC INFORMATICA SIGLO 21 LIMITADA</t>
         </is>
       </c>
       <c r="J206" t="inlineStr">
         <is>
-          <t>77.727.285-3</t>
-        </is>
-      </c>
-      <c r="K206" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.179.170-2</t>
+        </is>
+      </c>
+      <c r="K206" t="inlineStr"/>
       <c r="L206" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M206" s="2" t="n">
-        <v>995.64</v>
+        <v>15261.75</v>
       </c>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>2675-358-CM26</t>
+          <t>5543-47-CM26</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -13720,27 +13720,27 @@
       </c>
       <c r="F207" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G207" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H207" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I207" t="inlineStr">
         <is>
-          <t>TIC SERVICES SPA</t>
+          <t>ALEMED SOLUCIONES INTEGRALES SPA</t>
         </is>
       </c>
       <c r="J207" t="inlineStr">
         <is>
-          <t>76.423.634-3</t>
+          <t>77.727.285-3</t>
         </is>
       </c>
       <c r="K207" t="inlineStr">
@@ -13754,13 +13754,13 @@
         </is>
       </c>
       <c r="M207" s="2" t="n">
-        <v>2658.46</v>
+        <v>995.64</v>
       </c>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>2859-888-CM26</t>
+          <t>2675-358-CM26</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -13780,32 +13780,32 @@
       </c>
       <c r="E208" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F208" t="inlineStr">
         <is>
-          <t>71.236.700-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G208" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE ATACAMA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
         <is>
-          <t>Atacama</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I208" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>TIC SERVICES SPA</t>
         </is>
       </c>
       <c r="J208" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.423.634-3</t>
         </is>
       </c>
       <c r="K208" t="inlineStr">
@@ -13819,13 +13819,13 @@
         </is>
       </c>
       <c r="M208" s="2" t="n">
-        <v>7182.45</v>
+        <v>2658.46</v>
       </c>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>2675-357-CM26</t>
+          <t>2859-888-CM26</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -13850,43 +13850,47 @@
       </c>
       <c r="F209" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>71.236.700-8</t>
         </is>
       </c>
       <c r="G209" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>UNIVERSIDAD DE ATACAMA</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Atacama</t>
         </is>
       </c>
       <c r="I209" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>COMERCIALIZADORA TODOCLICK SPA</t>
         </is>
       </c>
       <c r="J209" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr"/>
+          <t>76.977.985-K</t>
+        </is>
+      </c>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L209" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M209" s="2" t="n">
-        <v>2284.8</v>
+        <v>7182.45</v>
       </c>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>3614-241-CM26</t>
+          <t>2675-357-CM26</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -13911,47 +13915,43 @@
       </c>
       <c r="F210" t="inlineStr">
         <is>
-          <t>69.040.500-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G210" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE VICUNA</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H210" t="inlineStr">
         <is>
-          <t>Coquimbo</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I210" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J210" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr"/>
       <c r="L210" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M210" s="2" t="n">
-        <v>4746.03</v>
+        <v>2284.8</v>
       </c>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>2675-354-CM26</t>
+          <t>3614-241-CM26</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -13976,27 +13976,27 @@
       </c>
       <c r="F211" t="inlineStr">
         <is>
-          <t>69.080.500-6</t>
+          <t>69.040.500-8</t>
         </is>
       </c>
       <c r="G211" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
+          <t>I MUNICIPALIDAD DE VICUNA</t>
         </is>
       </c>
       <c r="H211" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Coquimbo</t>
         </is>
       </c>
       <c r="I211" t="inlineStr">
         <is>
-          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J211" t="inlineStr">
         <is>
-          <t>77.508.642-4</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K211" t="inlineStr">
@@ -14010,13 +14010,13 @@
         </is>
       </c>
       <c r="M211" s="2" t="n">
-        <v>4574.96</v>
+        <v>4746.03</v>
       </c>
     </row>
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>3244-334-CM26</t>
+          <t>2675-354-CM26</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -14041,27 +14041,27 @@
       </c>
       <c r="F212" t="inlineStr">
         <is>
-          <t>69.073.500-8</t>
+          <t>69.080.500-6</t>
         </is>
       </c>
       <c r="G212" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
+          <t>I MUNICIPALIDAD DE MOSTAZAL</t>
         </is>
       </c>
       <c r="H212" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I212" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>VENTA, COMPRAS DE EQUIPOS &amp; ACCESORIOS TECNOLOGICOS SPA</t>
         </is>
       </c>
       <c r="J212" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>77.508.642-4</t>
         </is>
       </c>
       <c r="K212" t="inlineStr">
@@ -14075,13 +14075,13 @@
         </is>
       </c>
       <c r="M212" s="2" t="n">
-        <v>11138.4</v>
+        <v>4574.96</v>
       </c>
     </row>
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>1305527-34-CM26</t>
+          <t>3244-334-CM26</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -14106,43 +14106,47 @@
       </c>
       <c r="F213" t="inlineStr">
         <is>
-          <t>61.981.090-2</t>
+          <t>69.073.500-8</t>
         </is>
       </c>
       <c r="G213" t="inlineStr">
         <is>
-          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
+          <t>I MUNICIPALIDAD DE SANTO DOMINGO</t>
         </is>
       </c>
       <c r="H213" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I213" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J213" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K213" t="inlineStr"/>
+          <t>76.416.101-7</t>
+        </is>
+      </c>
+      <c r="K213" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L213" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M213" s="2" t="n">
-        <v>4997.98</v>
+        <v>11138.4</v>
       </c>
     </row>
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>5434-288-CM26</t>
+          <t>1305527-34-CM26</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -14157,7 +14161,7 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>2026-08-21</t>
+          <t>2026-08-20</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -14167,12 +14171,12 @@
       </c>
       <c r="F214" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.981.090-2</t>
         </is>
       </c>
       <c r="G214" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>SERVICIO LOCAL DE EDUCACIÓN PÚBLICA DEL PINO</t>
         </is>
       </c>
       <c r="H214" t="inlineStr">
@@ -14182,32 +14186,28 @@
       </c>
       <c r="I214" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J214" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>79.882.360-4</t>
+        </is>
+      </c>
+      <c r="K214" t="inlineStr"/>
       <c r="L214" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M214" s="2" t="n">
-        <v>2380.98</v>
+        <v>4997.98</v>
       </c>
     </row>
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>1019-284-CM26</t>
+          <t>5434-288-CM26</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -14227,17 +14227,17 @@
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
         <is>
-          <t>61.202.000-0</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G215" t="inlineStr">
         <is>
-          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H215" t="inlineStr">
@@ -14266,13 +14266,13 @@
         </is>
       </c>
       <c r="M215" s="2" t="n">
-        <v>1395.04</v>
+        <v>2380.98</v>
       </c>
     </row>
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>5839-38-CM26</t>
+          <t>1019-284-CM26</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -14292,32 +14292,32 @@
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
         <is>
-          <t>61.102.016-3</t>
+          <t>61.202.000-0</t>
         </is>
       </c>
       <c r="G216" t="inlineStr">
         <is>
-          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
+          <t>MINISTERIO DE OBRAS PUBLICAS DIREC CION GRAL DE OO PP DCYF</t>
         </is>
       </c>
       <c r="H216" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I216" t="inlineStr">
         <is>
-          <t>SANDOS SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J216" t="inlineStr">
         <is>
-          <t>77.319.537-4</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K216" t="inlineStr">
@@ -14331,13 +14331,13 @@
         </is>
       </c>
       <c r="M216" s="2" t="n">
-        <v>30421.76</v>
+        <v>1395.04</v>
       </c>
     </row>
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>1233666-40-CM26</t>
+          <t>5839-38-CM26</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -14362,27 +14362,27 @@
       </c>
       <c r="F217" t="inlineStr">
         <is>
-          <t>65.172.583-6</t>
+          <t>61.102.016-3</t>
         </is>
       </c>
       <c r="G217" t="inlineStr">
         <is>
-          <t>Corporación Municipal de Innovación y Desarrollo Económico y Social de Recoleta</t>
+          <t>DIRECCION DE ABASTECIMIENTO DE LA ARMADA</t>
         </is>
       </c>
       <c r="H217" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I217" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>SANDOS SPA</t>
         </is>
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>77.319.537-4</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
@@ -14396,13 +14396,13 @@
         </is>
       </c>
       <c r="M217" s="2" t="n">
-        <v>1587.32</v>
+        <v>30421.76</v>
       </c>
     </row>
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>1233666-39-CM26</t>
+          <t>1233666-40-CM26</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -14442,28 +14442,32 @@
       </c>
       <c r="I218" t="inlineStr">
         <is>
-          <t>Sumatec Ltda.</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J218" t="inlineStr">
         <is>
-          <t>76.367.430-4</t>
-        </is>
-      </c>
-      <c r="K218" t="inlineStr"/>
+          <t>78.114.650-1</t>
+        </is>
+      </c>
+      <c r="K218" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L218" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M218" s="2" t="n">
-        <v>2276.8</v>
+        <v>1587.32</v>
       </c>
     </row>
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>1501728-55-CM26</t>
+          <t>1233666-39-CM26</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -14483,52 +14487,48 @@
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
         <is>
-          <t>69.081.100-6</t>
+          <t>65.172.583-6</t>
         </is>
       </c>
       <c r="G219" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
+          <t>Corporación Municipal de Innovación y Desarrollo Económico y Social de Recoleta</t>
         </is>
       </c>
       <c r="H219" t="inlineStr">
         <is>
-          <t>O'Higgins</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I219" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>Sumatec Ltda.</t>
         </is>
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
-        </is>
-      </c>
-      <c r="K219" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.367.430-4</t>
+        </is>
+      </c>
+      <c r="K219" t="inlineStr"/>
       <c r="L219" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M219" s="2" t="n">
-        <v>14183.69</v>
+        <v>2276.8</v>
       </c>
     </row>
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>5434-281-CM26</t>
+          <t>1501728-55-CM26</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
@@ -14553,43 +14553,47 @@
       </c>
       <c r="F220" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.081.100-6</t>
         </is>
       </c>
       <c r="G220" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE PICHIDEGUA</t>
         </is>
       </c>
       <c r="H220" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>O'Higgins</t>
         </is>
       </c>
       <c r="I220" t="inlineStr">
         <is>
-          <t>PC FACTORY</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J220" t="inlineStr">
         <is>
-          <t>78.885.550-8</t>
-        </is>
-      </c>
-      <c r="K220" t="inlineStr"/>
+          <t>76.376.530-k</t>
+        </is>
+      </c>
+      <c r="K220" t="inlineStr">
+        <is>
+          <t>Metropolitana</t>
+        </is>
+      </c>
       <c r="L220" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M220" s="2" t="n">
-        <v>296.31</v>
+        <v>14183.69</v>
       </c>
     </row>
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>5434-279-CM26</t>
+          <t>5434-281-CM26</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -14609,7 +14613,7 @@
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -14629,32 +14633,28 @@
       </c>
       <c r="I221" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>PC FACTORY</t>
         </is>
       </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
-        </is>
-      </c>
-      <c r="K221" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>78.885.550-8</t>
+        </is>
+      </c>
+      <c r="K221" t="inlineStr"/>
       <c r="L221" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M221" s="2" t="n">
-        <v>793.66</v>
+        <v>296.31</v>
       </c>
     </row>
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>1057461-1342-CM26</t>
+          <t>5434-279-CM26</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
@@ -14674,37 +14674,37 @@
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>61.606.913-6</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G222" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H222" t="inlineStr">
         <is>
-          <t>Maule</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I222" t="inlineStr">
         <is>
-          <t>IMPORTADORA HEVIA SPA</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J222" t="inlineStr">
         <is>
-          <t>76.872.717-1</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K222" t="inlineStr">
         <is>
-          <t>Biobío</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
@@ -14713,13 +14713,13 @@
         </is>
       </c>
       <c r="M222" s="2" t="n">
-        <v>18046.35</v>
+        <v>793.66</v>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>3091-110-CM26</t>
+          <t>1057461-1342-CM26</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -14739,37 +14739,37 @@
       </c>
       <c r="E223" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F223" t="inlineStr">
         <is>
-          <t>69.061.400-6</t>
+          <t>61.606.913-6</t>
         </is>
       </c>
       <c r="G223" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE CASABLANCA</t>
+          <t>SERVICIO DE SALUD DEL MAULE HOSPITAL DE CAUQUENES</t>
         </is>
       </c>
       <c r="H223" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Maule</t>
         </is>
       </c>
       <c r="I223" t="inlineStr">
         <is>
-          <t>COMPUTACION INTEGRAL S A</t>
+          <t>IMPORTADORA HEVIA SPA</t>
         </is>
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>96.689.970-0</t>
+          <t>76.872.717-1</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Biobío</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
@@ -14778,13 +14778,13 @@
         </is>
       </c>
       <c r="M223" s="2" t="n">
-        <v>6097</v>
+        <v>18046.35</v>
       </c>
     </row>
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>5526-55-CM26</t>
+          <t>3091-110-CM26</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -14809,32 +14809,32 @@
       </c>
       <c r="F224" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>69.061.400-6</t>
         </is>
       </c>
       <c r="G224" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>I MUNICIPALIDAD DE CASABLANCA</t>
         </is>
       </c>
       <c r="H224" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="I224" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
+          <t>COMPUTACION INTEGRAL S A</t>
         </is>
       </c>
       <c r="J224" t="inlineStr">
         <is>
-          <t>77.474.803-2</t>
+          <t>96.689.970-0</t>
         </is>
       </c>
       <c r="K224" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Valparaíso</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
@@ -14843,13 +14843,13 @@
         </is>
       </c>
       <c r="M224" s="2" t="n">
-        <v>2022.98</v>
+        <v>6097</v>
       </c>
     </row>
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>5807-161-CM26</t>
+          <t>5526-55-CM26</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -14864,12 +14864,12 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>2026-08-24</t>
+          <t>2026-08-21</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F225" t="inlineStr">
@@ -14889,28 +14889,32 @@
       </c>
       <c r="I225" t="inlineStr">
         <is>
-          <t>I.I.A. Ltda.</t>
+          <t>COMERCIALIZADORA SANTA CATALINA SPA</t>
         </is>
       </c>
       <c r="J225" t="inlineStr">
         <is>
-          <t>79.882.360-4</t>
-        </is>
-      </c>
-      <c r="K225" t="inlineStr"/>
+          <t>77.474.803-2</t>
+        </is>
+      </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
       <c r="L225" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M225" s="2" t="n">
-        <v>1428</v>
+        <v>2022.98</v>
       </c>
     </row>
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>1154491-5-CM26</t>
+          <t>5807-161-CM26</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -14935,12 +14939,12 @@
       </c>
       <c r="F226" t="inlineStr">
         <is>
-          <t>61.216.000-7</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G226" t="inlineStr">
         <is>
-          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H226" t="inlineStr">
@@ -14950,12 +14954,12 @@
       </c>
       <c r="I226" t="inlineStr">
         <is>
-          <t>Sociedad Comercial Infostore Ltda</t>
+          <t>I.I.A. Ltda.</t>
         </is>
       </c>
       <c r="J226" t="inlineStr">
         <is>
-          <t>76.131.929-9</t>
+          <t>79.882.360-4</t>
         </is>
       </c>
       <c r="K226" t="inlineStr"/>
@@ -14965,13 +14969,13 @@
         </is>
       </c>
       <c r="M226" s="2" t="n">
-        <v>13470.19</v>
+        <v>1428</v>
       </c>
     </row>
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>5807-160-CM26</t>
+          <t>1154491-5-CM26</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -14996,12 +15000,12 @@
       </c>
       <c r="F227" t="inlineStr">
         <is>
-          <t>60.910.000-1</t>
+          <t>61.216.000-7</t>
         </is>
       </c>
       <c r="G227" t="inlineStr">
         <is>
-          <t>UNIVERSIDAD DE CHILE</t>
+          <t>EMPRESA DE LOS FERROCARRILES DEL ESTADO</t>
         </is>
       </c>
       <c r="H227" t="inlineStr">
@@ -15011,12 +15015,12 @@
       </c>
       <c r="I227" t="inlineStr">
         <is>
-          <t>FRANCO</t>
+          <t>Sociedad Comercial Infostore Ltda</t>
         </is>
       </c>
       <c r="J227" t="inlineStr">
         <is>
-          <t>76.139.769-9</t>
+          <t>76.131.929-9</t>
         </is>
       </c>
       <c r="K227" t="inlineStr"/>
@@ -15026,13 +15030,13 @@
         </is>
       </c>
       <c r="M227" s="2" t="n">
-        <v>1856.39</v>
+        <v>13470.19</v>
       </c>
     </row>
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>507428-880-CM26</t>
+          <t>2727-733-CM26</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -15052,32 +15056,32 @@
       </c>
       <c r="E228" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F228" t="inlineStr">
         <is>
-          <t>61.979.210-6</t>
+          <t>69.140.500-1</t>
         </is>
       </c>
       <c r="G228" t="inlineStr">
         <is>
-          <t>SERVICIO DE SALUD CHILOE</t>
+          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
         </is>
       </c>
       <c r="H228" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Ñuble</t>
         </is>
       </c>
       <c r="I228" t="inlineStr">
         <is>
-          <t>ARTEC INVERSIONES LIMITADA</t>
+          <t>NET NOW S.A.</t>
         </is>
       </c>
       <c r="J228" t="inlineStr">
         <is>
-          <t>76.416.101-7</t>
+          <t>78.112.170-3</t>
         </is>
       </c>
       <c r="K228" t="inlineStr">
@@ -15091,13 +15095,13 @@
         </is>
       </c>
       <c r="M228" s="2" t="n">
-        <v>4641</v>
+        <v>15820.1</v>
       </c>
     </row>
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>633-502-CM26</t>
+          <t>507428-880-CM26</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -15122,27 +15126,27 @@
       </c>
       <c r="F229" t="inlineStr">
         <is>
-          <t>61.313.000-4</t>
+          <t>61.979.210-6</t>
         </is>
       </c>
       <c r="G229" t="inlineStr">
         <is>
-          <t>CORP NACIONAL FORESTAL</t>
+          <t>SERVICIO DE SALUD CHILOE</t>
         </is>
       </c>
       <c r="H229" t="inlineStr">
         <is>
-          <t>Metropolitana</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I229" t="inlineStr">
         <is>
-          <t>LECHNER S.A</t>
+          <t>ARTEC INVERSIONES LIMITADA</t>
         </is>
       </c>
       <c r="J229" t="inlineStr">
         <is>
-          <t>78.114.650-1</t>
+          <t>76.416.101-7</t>
         </is>
       </c>
       <c r="K229" t="inlineStr">
@@ -15156,13 +15160,13 @@
         </is>
       </c>
       <c r="M229" s="2" t="n">
-        <v>1587.32</v>
+        <v>4641</v>
       </c>
     </row>
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>2727-733-CM26</t>
+          <t>5807-160-CM26</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -15182,52 +15186,48 @@
       </c>
       <c r="E230" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F230" t="inlineStr">
         <is>
-          <t>69.140.500-1</t>
+          <t>60.910.000-1</t>
         </is>
       </c>
       <c r="G230" t="inlineStr">
         <is>
-          <t>ILUSTRE MUNICIPALIDAD DE SAN CARLOS</t>
+          <t>UNIVERSIDAD DE CHILE</t>
         </is>
       </c>
       <c r="H230" t="inlineStr">
         <is>
-          <t>Ñuble</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I230" t="inlineStr">
         <is>
-          <t>NET NOW S.A.</t>
+          <t>FRANCO</t>
         </is>
       </c>
       <c r="J230" t="inlineStr">
         <is>
-          <t>78.112.170-3</t>
-        </is>
-      </c>
-      <c r="K230" t="inlineStr">
-        <is>
-          <t>Metropolitana</t>
-        </is>
-      </c>
+          <t>76.139.769-9</t>
+        </is>
+      </c>
+      <c r="K230" t="inlineStr"/>
       <c r="L230" t="inlineStr">
         <is>
           <t>USD</t>
         </is>
       </c>
       <c r="M230" s="2" t="n">
-        <v>15820.1</v>
+        <v>1856.39</v>
       </c>
     </row>
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>3561-399-CM26</t>
+          <t>2324-1140-CM26</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -15247,32 +15247,32 @@
       </c>
       <c r="E231" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F231" t="inlineStr">
         <is>
-          <t>69.060.300-4</t>
+          <t>69.220.100-0</t>
         </is>
       </c>
       <c r="G231" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE LA CALERA</t>
+          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
         </is>
       </c>
       <c r="H231" t="inlineStr">
         <is>
-          <t>Valparaíso</t>
+          <t>Los Lagos</t>
         </is>
       </c>
       <c r="I231" t="inlineStr">
         <is>
-          <t>COMERCIALIZADORA TODOCLICK SPA</t>
+          <t>BOOKCOMPUTER</t>
         </is>
       </c>
       <c r="J231" t="inlineStr">
         <is>
-          <t>76.977.985-K</t>
+          <t>76.376.530-k</t>
         </is>
       </c>
       <c r="K231" t="inlineStr">
@@ -15286,7 +15286,7 @@
         </is>
       </c>
       <c r="M231" s="2" t="n">
-        <v>3597.95</v>
+        <v>4239.14</v>
       </c>
     </row>
     <row r="232">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -15483,7 +15483,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>2324-1140-CM26</t>
+          <t>633-502-CM26</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -15503,32 +15503,32 @@
       </c>
       <c r="E235" t="inlineStr">
         <is>
-          <t>Recepcion Conforme</t>
+          <t>Aceptada</t>
         </is>
       </c>
       <c r="F235" t="inlineStr">
         <is>
-          <t>69.220.100-0</t>
+          <t>61.313.000-4</t>
         </is>
       </c>
       <c r="G235" t="inlineStr">
         <is>
-          <t>I MUNICIPALIDAD DE PUERTO MONTT</t>
+          <t>CORP NACIONAL FORESTAL</t>
         </is>
       </c>
       <c r="H235" t="inlineStr">
         <is>
-          <t>Los Lagos</t>
+          <t>Metropolitana</t>
         </is>
       </c>
       <c r="I235" t="inlineStr">
         <is>
-          <t>BOOKCOMPUTER</t>
+          <t>LECHNER S.A</t>
         </is>
       </c>
       <c r="J235" t="inlineStr">
         <is>
-          <t>76.376.530-k</t>
+          <t>78.114.650-1</t>
         </is>
       </c>
       <c r="K235" t="inlineStr">
@@ -15542,7 +15542,7 @@
         </is>
       </c>
       <c r="M235" s="2" t="n">
-        <v>4239.14</v>
+        <v>1587.32</v>
       </c>
     </row>
     <row r="236">
@@ -15633,7 +15633,7 @@
       </c>
       <c r="E237" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F237" t="inlineStr">
@@ -17665,7 +17665,7 @@
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E273" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F273" t="inlineStr">
@@ -18169,7 +18169,7 @@
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -19445,7 +19445,7 @@
       </c>
       <c r="E297" t="inlineStr">
         <is>
-          <t>Aceptada</t>
+          <t>Recepcion Conforme</t>
         </is>
       </c>
       <c r="F297" t="inlineStr">
